--- a/04_DESIGN_TABLES/DesignTable_6501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6501_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI12"/>
+  <dimension ref="A1:BI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,13 +869,13 @@
         <v>0.28</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.16166</v>
+        <v>0.16116</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.32332</v>
+        <v>0.32282</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1069,13 +1069,13 @@
         <v>0.281</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.16224</v>
+        <v>0.16174</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.32447</v>
+        <v>0.32397</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         <v>0.375</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6501-06-08-FG</t>
+          <t>6501-06-06-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1353,64 +1353,64 @@
         <v>0.1522</v>
       </c>
       <c r="H5" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="I5" t="n">
         <v>0.375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.885</v>
+        <v>0.785</v>
       </c>
       <c r="K5" t="n">
-        <v>0.292</v>
+        <v>0.206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.827</v>
+        <v>0.735</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4108</v>
+        <v>0.3224</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4361</v>
+        <v>0.3428</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.50518</v>
+        <v>0.39722</v>
       </c>
       <c r="R5" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3283</v>
+        <v>0.2945</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3925</v>
+        <v>0.2925</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6723</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.34</v>
+        <v>0.246</v>
       </c>
       <c r="X5" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2825</v>
+        <v>0.215</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.875</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="AB5" t="n">
         <v>0.406</v>
@@ -1419,10 +1419,10 @@
         <v>1.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.391</v>
+        <v>0.297</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AF5" t="n">
         <v>0.65645</v>
@@ -1443,22 +1443,22 @@
         <v>1.22</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.3567</v>
+        <v>0.3197</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AR5" t="n">
         <v>0.75</v>
@@ -1479,22 +1479,22 @@
         <v>0.375</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.21651</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.43301</v>
+        <v>0.43251</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6501-06-08-FG</t>
+          <t>6501-06-06-FG</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 3/8-18 NPTF x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 3/8-18 NPTF x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -1519,187 +1519,187 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-06-08 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1945 L 1 Size = 1.220 (table had empty); M5@DRIVE: OMi Items!O1945 M 2 Size = 1.380 (table had empty); M10@DRIVE: OMi Items!N1945 M 1 Size = 0.960 (table had empty); C3HEX@HEX: OMi Items!V1945 Nut Hex 1 = 0.875 (table had empty); Y@HEX: OMi Items!R1945 Hex Flat = 0.750 (table had empty); D1@BORE: OMi Items!S1945 Side 1 ID = 0.406 (table had empty); D@BORE: OMi Items!X1945 Side 2 ID = 0.391 (table had empty); THDMAJ_A@DRIVE: 3/8-18 -&gt; 0.675 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-06-08-FG row = OMi on every cell (rounding only: M10@DRIVE: catalog M4 LGTH 0.958 vs OMi 0.960 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-06-06 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): N@DRIVE: OMi Items row 1944 L 1 Size = 1.220; M5@DRIVE: OMi Items row 1944 M 2 Size = 1.280; M10@DRIVE: OMi Items row 1944 M 1 Size = 0.910; C3HEX@HEX: OMi Items row 1944 Nut Hex 1 = 0.688; Y@HEX: OMi Items row 1944 Hex Flat = 0.750; D1@BORE: OMi Items row 1944 Side 1 ID = 0.406; D@BORE: OMi Items row 1944 Side 2 ID = 0.297; THDMAJ_A@DRIVE: 3/8-18 -&gt; 0.675 (end library); THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male pipe leg (catalog N), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 ID = pipe-end bore, Side 2 ID = swivel bore (batch-15 pairing, Brennan TFA p35 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-06-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1945 (= Brennan TFA p35 6501-06-08-FG, one source) - ASSUMED; catalog rounding-only prints: M10@DRIVE: catalog M4 LGTH 0.958 vs OMi 0.960 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1944 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p035-t01: TUBE O.D. 3/8, A NPTF 3/8-18, B SAE 37Deg 9/16-18, A DRILL 0.406, B DRILL 0.297, M4 LGTH 0.90, M6 LGTH 1.28, N LGTH 1.22, C HEX 0.688, Y FLATS 0.750</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>6501-06-08-FG</t>
+          <t>6501-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6501-08-06-FG</t>
+          <t>6501-06-08-FG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="D6" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="F6" t="n">
         <v>1.7899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="H6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="J6" t="n">
-        <v>0.785</v>
+        <v>0.885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.206</v>
+        <v>0.292</v>
       </c>
       <c r="L6" t="n">
-        <v>0.735</v>
+        <v>0.827</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3224</v>
+        <v>0.4108</v>
       </c>
       <c r="N6" t="n">
-        <v>0.145</v>
+        <v>0.18</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3428</v>
+        <v>0.4361</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3876</v>
+        <v>0.4499</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.39722</v>
+        <v>0.50518</v>
       </c>
       <c r="R6" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="S6" t="n">
-        <v>0.25118</v>
+        <v>0.34117</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2945</v>
+        <v>0.3283</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2925</v>
+        <v>0.3925</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.6723</v>
       </c>
       <c r="W6" t="n">
-        <v>0.246</v>
+        <v>0.34</v>
       </c>
       <c r="X6" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.215</v>
+        <v>0.2825</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3876</v>
+        <v>0.4499</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.531</v>
+        <v>0.406</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.297</v>
+        <v>0.391</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.50236</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.3197</v>
+        <v>0.3567</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.25118</v>
+        <v>0.34117</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.635</v>
+        <v>0.495</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.25259</v>
+        <v>0.21601</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.25259</v>
+        <v>0.21601</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.50518</v>
+        <v>0.43251</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6501-08-06-FG</t>
+          <t>6501-06-08-FG</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 1/2-14 NPTF x 9/16-18 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 3/8-18 NPTF x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>9/16-18 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-08-06 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1946 L 1 Size = 1.470 (table had empty); M5@DRIVE: OMi Items!O1946 M 2 Size = 1.420 (table had empty); M10@DRIVE: OMi Items!N1946 M 1 Size = 1.050 (table had empty); C3HEX@HEX: OMi Items!V1946 Nut Hex 1 = 0.688 (table had empty); Y@HEX: OMi Items!R1946 Hex Flat = 0.875 (table had empty); D1@BORE: OMi Items!S1946 Side 1 ID = 0.531 (table had empty); D@BORE: OMi Items!X1946 Side 2 ID = 0.297 (table had empty); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-08-06-FG row = OMi on every cell (rounding only: M10@DRIVE: catalog M4 LGTH 1.045 vs OMi 1.050 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-06-08 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1945 L 1 Size = 1.220 (table had empty); M5@DRIVE: OMi Items!O1945 M 2 Size = 1.380 (table had empty); M10@DRIVE: OMi Items!N1945 M 1 Size = 0.960 (table had empty); C3HEX@HEX: OMi Items!V1945 Nut Hex 1 = 0.875 (table had empty); Y@HEX: OMi Items!R1945 Hex Flat = 0.750 (table had empty); D1@BORE: OMi Items!S1945 Side 1 ID = 0.406 (table had empty); D@BORE: OMi Items!X1945 Side 2 ID = 0.391 (table had empty); THDMAJ_A@DRIVE: 3/8-18 -&gt; 0.675 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-06-08-FG row = OMi on every cell (rounding only: M10@DRIVE: catalog M4 LGTH 0.958 vs OMi 0.960 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-08-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1946 (= Brennan TFA p35 6501-08-06-FG, one source) - ASSUMED; catalog rounding-only prints: M10@DRIVE: catalog M4 LGTH 1.045 vs OMi 1.050 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-06-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1945 (= Brennan TFA p35 6501-06-08-FG, one source) - ASSUMED; catalog rounding-only prints: M10@DRIVE: catalog M4 LGTH 0.958 vs OMi 0.960 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex)</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>6501-08-06-FG</t>
+          <t>6501-06-08-FG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6501-08-08-FG</t>
+          <t>6501-08-06-FG</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1763,64 +1763,64 @@
         <v>0.2163</v>
       </c>
       <c r="H7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="I7" t="n">
         <v>0.4375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.885</v>
+        <v>0.785</v>
       </c>
       <c r="K7" t="n">
-        <v>0.292</v>
+        <v>0.206</v>
       </c>
       <c r="L7" t="n">
-        <v>0.827</v>
+        <v>0.735</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4108</v>
+        <v>0.3224</v>
       </c>
       <c r="N7" t="n">
-        <v>0.18</v>
+        <v>0.145</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4361</v>
+        <v>0.3428</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.50518</v>
+        <v>0.39722</v>
       </c>
       <c r="R7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="S7" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3283</v>
+        <v>0.2945</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3925</v>
+        <v>0.2925</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6723</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.34</v>
+        <v>0.246</v>
       </c>
       <c r="X7" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2825</v>
+        <v>0.215</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.875</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4499</v>
+        <v>0.3876</v>
       </c>
       <c r="AB7" t="n">
         <v>0.531</v>
@@ -1829,10 +1829,10 @@
         <v>1.47</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.391</v>
+        <v>0.297</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
         <v>0.81557</v>
@@ -1853,22 +1853,22 @@
         <v>1.47</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.6823399999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.3567</v>
+        <v>0.3197</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.34117</v>
+        <v>0.25118</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AR7" t="n">
         <v>0.875</v>
@@ -1889,22 +1889,22 @@
         <v>0.4375</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.50518</v>
+        <v>0.50468</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6501-08-08-FG</t>
+          <t>6501-08-06-FG</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 1/2-14 NPTF x 3/4-16 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 1/2-14 NPTF x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>3/4-16 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -1929,24 +1929,24 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-08-08 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1947 L 1 Size = 1.470 (table had empty); M5@DRIVE: OMi Items!O1947 M 2 Size = 1.520 (table had empty); M10@DRIVE: OMi Items!N1947 M 1 Size = 1.090 (table had empty); C3HEX@HEX: OMi Items!V1947 Nut Hex 1 = 0.875 (table had empty); Y@HEX: OMi Items!R1947 Hex Flat = 0.875 (table had empty); D1@BORE: OMi Items!S1947 Side 1 ID = 0.531 (table had empty); D@BORE: OMi Items!X1947 Side 2 ID = 0.391 (table had empty); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-08-08-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-08-06 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1946 L 1 Size = 1.470 (table had empty); M5@DRIVE: OMi Items!O1946 M 2 Size = 1.420 (table had empty); M10@DRIVE: OMi Items!N1946 M 1 Size = 1.050 (table had empty); C3HEX@HEX: OMi Items!V1946 Nut Hex 1 = 0.688 (table had empty); Y@HEX: OMi Items!R1946 Hex Flat = 0.875 (table had empty); D1@BORE: OMi Items!S1946 Side 1 ID = 0.531 (table had empty); D@BORE: OMi Items!X1946 Side 2 ID = 0.297 (table had empty); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-08-06-FG row = OMi on every cell (rounding only: M10@DRIVE: catalog M4 LGTH 1.045 vs OMi 1.050 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1947 (= Brennan TFA p35 6501-08-08-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT, Q-CALIPER (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex; Q-CALIPER = caliper readings)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-08-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1946 (= Brennan TFA p35 6501-08-06-FG, one source) - ASSUMED; catalog rounding-only prints: M10@DRIVE: catalog M4 LGTH 1.045 vs OMi 1.050 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex)</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>6501-08-08-FG</t>
+          <t>6501-08-06-FG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6501-08-10-FG</t>
+          <t>6501-08-08-FG</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1968,64 +1968,64 @@
         <v>0.2163</v>
       </c>
       <c r="H8" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="I8" t="n">
         <v>0.4375</v>
       </c>
       <c r="J8" t="n">
-        <v>0.985</v>
+        <v>0.885</v>
       </c>
       <c r="K8" t="n">
-        <v>0.347</v>
+        <v>0.292</v>
       </c>
       <c r="L8" t="n">
-        <v>0.944</v>
+        <v>0.827</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4758</v>
+        <v>0.4108</v>
       </c>
       <c r="N8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4988</v>
+        <v>0.4361</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.57735</v>
+        <v>0.50518</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="S8" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="T8" t="n">
-        <v>0.404</v>
+        <v>0.3283</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4475</v>
+        <v>0.3925</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7794</v>
+        <v>0.6723</v>
       </c>
       <c r="W8" t="n">
-        <v>0.394</v>
+        <v>0.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3375</v>
+        <v>0.2825</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5265</v>
+        <v>0.4499</v>
       </c>
       <c r="AB8" t="n">
         <v>0.531</v>
@@ -2034,10 +2034,10 @@
         <v>1.47</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.484</v>
+        <v>0.391</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AF8" t="n">
         <v>0.81557</v>
@@ -2058,22 +2058,22 @@
         <v>1.47</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.4364</v>
+        <v>0.3567</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.39884</v>
+        <v>0.34117</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AR8" t="n">
         <v>0.875</v>
@@ -2094,22 +2094,22 @@
         <v>0.4375</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.25259</v>
+        <v>0.25209</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.50518</v>
+        <v>0.50468</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6501-08-10-FG</t>
+          <t>6501-08-08-FG</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 1/2-14 NPTF x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 1/2-14 NPTF x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -2134,187 +2134,187 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-08-10 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1948 L 1 Size = 1.470 (table had empty); M5@DRIVE: OMi Items!O1948 M 2 Size = 1.620 (table had empty); M10@DRIVE: OMi Items!N1948 M 1 Size = 1.120 (table had empty); C3HEX@HEX: OMi Items!V1948 Nut Hex 1 = 1.000 (table had empty); Y@HEX: OMi Items!R1948 Hex Flat = 0.875 (table had empty); D1@BORE: OMi Items!S1948 Side 1 ID = 0.531 (table had empty); D@BORE: OMi Items!X1948 Side 2 ID = 0.484 (table had empty); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 7/8-14 -&gt; 0.875 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-08-10-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-08-08 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1947 L 1 Size = 1.470 (table had empty); M5@DRIVE: OMi Items!O1947 M 2 Size = 1.520 (table had empty); M10@DRIVE: OMi Items!N1947 M 1 Size = 1.090 (table had empty); C3HEX@HEX: OMi Items!V1947 Nut Hex 1 = 0.875 (table had empty); Y@HEX: OMi Items!R1947 Hex Flat = 0.875 (table had empty); D1@BORE: OMi Items!S1947 Side 1 ID = 0.531 (table had empty); D@BORE: OMi Items!X1947 Side 2 ID = 0.391 (table had empty); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-08-08-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-08-10 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1948 (= Brennan TFA p35 6501-08-10-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1947 (= Brennan TFA p35 6501-08-08-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT, Q-CALIPER (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex; Q-CALIPER = caliper readings)</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>6501-08-10-FG</t>
+          <t>6501-08-08-FG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6501-16-16-FG</t>
+          <t>6501-08-10-FG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="C9" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="F9" t="n">
         <v>1.7899</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2572</v>
+        <v>0.2163</v>
       </c>
       <c r="H9" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="J9" t="n">
-        <v>1.175</v>
+        <v>0.985</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5485</v>
+        <v>0.347</v>
       </c>
       <c r="L9" t="n">
-        <v>1.139</v>
+        <v>0.944</v>
       </c>
       <c r="M9" t="n">
-        <v>0.727</v>
+        <v>0.4758</v>
       </c>
       <c r="N9" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>0.749</v>
+        <v>0.4988</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.86603</v>
+        <v>0.57735</v>
       </c>
       <c r="R9" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="S9" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4873</v>
+        <v>0.404</v>
       </c>
       <c r="U9" t="n">
-        <v>0.665</v>
+        <v>0.4475</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9544</v>
+        <v>0.7794</v>
       </c>
       <c r="W9" t="n">
-        <v>0.604</v>
+        <v>0.394</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5475</v>
+        <v>0.3375</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.6564</v>
+        <v>0.5265</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.844</v>
+        <v>0.484</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.2832</v>
+        <v>0.81557</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.6828</v>
+        <v>0.5337</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.40779</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.57203</v>
+        <v>0.35064</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.22228</v>
+        <v>0.7976799999999999</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5252</v>
+        <v>0.4364</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.61114</v>
+        <v>0.39884</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.65625</v>
+        <v>0.4375</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.312</v>
+        <v>0.875</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>0.72</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.312</v>
+        <v>0.875</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.835</v>
+        <v>0.635</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.656</v>
+        <v>0.4375</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.37874</v>
+        <v>0.25209</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.37874</v>
+        <v>0.25209</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.75748</v>
+        <v>0.50468</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6501-16-16-FG</t>
+          <t>6501-08-10-FG</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 1-11 1/2 NPTF x 1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 1/2-14 NPTF x 7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -2339,187 +2339,187 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-16-16 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1952 L 1 Size = 1.970 (table had empty); M5@DRIVE: OMi Items!O1952 M 2 Size = 2.010 (table had empty); M10@DRIVE: OMi Items!N1952 M 1 Size = 1.410 (table had empty); C3HEX@HEX: OMi Items!V1952 Nut Hex 1 = 1.500 (table had empty); Y@HEX: OMi Items!R1952 Hex Flat = 1.312 (table had empty); D1@BORE: OMi Items!S1952 Side 1 ID = 0.938 (table had empty); D@BORE: OMi Items!X1952 Side 2 ID = 0.844 (table had empty); THDMAJ_A@DRIVE: 1-11 1/2 -&gt; 1.315 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 1 5/16-12 -&gt; 1.3125 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-16-16-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-08-10 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1948 L 1 Size = 1.470 (table had empty); M5@DRIVE: OMi Items!O1948 M 2 Size = 1.620 (table had empty); M10@DRIVE: OMi Items!N1948 M 1 Size = 1.120 (table had empty); C3HEX@HEX: OMi Items!V1948 Nut Hex 1 = 1.000 (table had empty); Y@HEX: OMi Items!R1948 Hex Flat = 0.875 (table had empty); D1@BORE: OMi Items!S1948 Side 1 ID = 0.531 (table had empty); D@BORE: OMi Items!X1948 Side 2 ID = 0.484 (table had empty); THDMAJ_A@DRIVE: 1/2-14 -&gt; 0.84 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 7/8-14 -&gt; 0.875 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-08-10-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1952 (= Brennan TFA p35 6501-16-16-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3120 (round end proud of the flats by 0.0069; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-08-10 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1948 (= Brennan TFA p35 6501-08-10-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex)</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>6501-16-16-FG</t>
+          <t>6501-08-10-FG</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6501-20-20-FG</t>
+          <t>6501-12-08-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8125</v>
+        <v>0.531</v>
       </c>
       <c r="D10" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="F10" t="n">
         <v>1.7899</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2632</v>
+        <v>0.2043</v>
       </c>
       <c r="H10" t="n">
-        <v>2.31</v>
+        <v>1.54</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8125</v>
+        <v>0.531</v>
       </c>
       <c r="J10" t="n">
-        <v>1.26</v>
+        <v>0.885</v>
       </c>
       <c r="K10" t="n">
-        <v>0.68</v>
+        <v>0.292</v>
       </c>
       <c r="L10" t="n">
-        <v>1.145</v>
+        <v>0.827</v>
       </c>
       <c r="M10" t="n">
-        <v>0.949</v>
+        <v>0.4108</v>
       </c>
       <c r="N10" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9889</v>
+        <v>0.4361</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5375</v>
+        <v>0.4499</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.1547</v>
+        <v>0.50518</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8125</v>
+        <v>0.375</v>
       </c>
       <c r="S10" t="n">
-        <v>0.76739</v>
+        <v>0.34117</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4345</v>
+        <v>0.3283</v>
       </c>
       <c r="U10" t="n">
-        <v>0.88</v>
+        <v>0.3925</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9556</v>
+        <v>0.6723</v>
       </c>
       <c r="W10" t="n">
-        <v>0.766</v>
+        <v>0.34</v>
       </c>
       <c r="X10" t="n">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7025</v>
+        <v>0.2825</v>
       </c>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>0.875</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5375</v>
+        <v>0.4499</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.25</v>
+        <v>0.719</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.078</v>
+        <v>0.391</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.31</v>
+        <v>1.54</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6267</v>
+        <v>1.02482</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.7068</v>
+        <v>0.5457</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.81335</v>
+        <v>0.51241</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.74378</v>
+        <v>0.45527</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.38</v>
+        <v>1.59</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.53478</v>
+        <v>0.6823399999999999</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.4724</v>
+        <v>0.3567</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.08333</v>
+        <v>0.0625</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.76739</v>
+        <v>0.34117</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.8125</v>
+        <v>0.375</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.31</v>
+        <v>1.54</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.625</v>
+        <v>1.062</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.41</v>
+        <v>0.84</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.625</v>
+        <v>1.062</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.05</v>
+        <v>0.655</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.8125</v>
+        <v>0.531</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.8125</v>
+        <v>0.531</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.4691</v>
+        <v>0.30607</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.4691</v>
+        <v>0.30607</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.93819</v>
+        <v>0.61265</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6501-20-20-FG</t>
+          <t>6501-12-08-FG</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 1 1/4-11 1/2 NPTF x 1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 3/4-14 NPTF x 3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>3/4-16 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -2544,187 +2544,187 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-20-20 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1953 L 1 Size = 2.380 (table had empty); M5@DRIVE: OMi Items!O1953 M 2 Size = 2.310 (table had empty); M10@DRIVE: OMi Items!N1953 M 1 Size = 1.670 (table had empty); C3HEX@HEX: OMi Items!V1953 Nut Hex 1 = 2.000 (table had empty); Y@HEX: OMi Items!R1953 Hex Flat = 1.625 (table had empty); D1@BORE: OMi Items!S1953 Side 1 ID = 1.250 (table had empty); D@BORE: OMi Items!X1953 Side 2 ID = 1.078 (table had empty); THDMAJ_A@DRIVE: 1 1/4-11 1/2 -&gt; 1.66 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 1 5/8-12 -&gt; 1.625 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-20-20-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; 2026-10-09 (left out of batch 15, staged): N@DRIVE: OMi Items row 1949 L 1 Size = 1.590; M5@DRIVE: OMi Items row 1949 M 2 Size = 1.540; M10@DRIVE: OMi Items row 1949 M 1 Size = 1.120; C3HEX@HEX: OMi Items row 1949 Nut Hex 1 = 0.875; Y@HEX: OMi Items row 1949 Hex Flat = 1.062; D1@BORE: OMi Items row 1949 Side 1 ID = 0.719; D@BORE: OMi Items row 1949 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 3/4-14 -&gt; 1.05 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male pipe leg (catalog N), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 ID = pipe-end bore, Side 2 ID = swivel bore (batch-15 pairing, Brennan TFA p35 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1953 (= Brennan TFA p35 6501-20-20-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1949 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p035-t01: TUBE O.D. 3/4, A NPTF 3/4-14, B SAE 37Deg 3/4-16, A DRILL 0.719, B DRILL 0.391, M4 LGTH 1.120, M6 LGTH 1.612, N LGTH 1.590, C HEX 0.875, Y FLATS 1.062 | leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0620 (round end flush with the flats by 0.0015; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>6501-20-20-FG</t>
+          <t>6501-12-08-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6501-24-24-FG</t>
+          <t>6501-12-12-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.64</v>
+        <v>1.59</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9375</v>
+        <v>0.5315</v>
       </c>
       <c r="D11" t="n">
-        <v>0.93283</v>
+        <v>0.51241</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7235</v>
+        <v>0.5457</v>
       </c>
       <c r="F11" t="n">
         <v>1.7899</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2765</v>
+        <v>0.2043</v>
       </c>
       <c r="H11" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9375</v>
+        <v>0.5315</v>
       </c>
       <c r="J11" t="n">
-        <v>1.41</v>
+        <v>1.089</v>
       </c>
       <c r="K11" t="n">
-        <v>0.776</v>
+        <v>0.417</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.047</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0504</v>
+        <v>0.5928</v>
       </c>
       <c r="N11" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.1134</v>
+        <v>0.6237</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7063</v>
+        <v>0.5998</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.29904</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="S11" t="n">
-        <v>0.89239</v>
+        <v>0.48614</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5295</v>
+        <v>0.4472</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>0.549</v>
       </c>
       <c r="V11" t="n">
-        <v>1.065</v>
+        <v>0.8623</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8885</v>
+        <v>0.481</v>
       </c>
       <c r="X11" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.4225</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.7063</v>
+        <v>0.5998</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0.719</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.64</v>
+        <v>1.59</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.312</v>
+        <v>0.609</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86566</v>
+        <v>1.02482</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.7235</v>
+        <v>0.5457</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.93283</v>
+        <v>0.51241</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.86326</v>
+        <v>0.45527</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.64</v>
+        <v>1.59</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.78478</v>
+        <v>0.97228</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5674</v>
+        <v>0.4851</v>
       </c>
       <c r="AN11" t="n">
         <v>0.08333</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.89239</v>
+        <v>0.48614</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.9375</v>
+        <v>0.53125</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.875</v>
+        <v>1.063</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.64</v>
+        <v>0.84</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.875</v>
+        <v>1.063</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.18</v>
+        <v>0.661</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.9375</v>
+        <v>0.5315</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9375</v>
+        <v>0.5315</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.54127</v>
+        <v>0.30636</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.54127</v>
+        <v>0.30636</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.08253</v>
+        <v>0.61322</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6501-24-24-FG</t>
+          <t>6501-12-12-FG</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>90 deg Male Pipe x Female Swivel Elbow, 1 1/2-11 1/2 NPTF x 1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 3/4-14 NPTF x 1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -2749,220 +2749,835 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-24-24 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1954 L 1 Size = 2.640 (table had empty); M5@DRIVE: OMi Items!O1954 M 2 Size = 2.590 (table had empty); M10@DRIVE: OMi Items!N1954 M 1 Size = 1.860 (table had empty); C3HEX@HEX: OMi Items!V1954 Nut Hex 1 = 2.250 (table had empty); Y@HEX: OMi Items!R1954 Hex Flat = 1.875 (table had empty); D1@BORE: OMi Items!S1954 Side 1 ID = 1.500 (table had empty); D@BORE: OMi Items!X1954 Side 2 ID = 1.312 (table had empty); THDMAJ_A@DRIVE: 1 1/2-11 1/2 -&gt; 1.9 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 1 7/8-12 -&gt; 1.875 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-24-24-FG row = OMi on every cell (rounding only: M10@DRIVE: catalog M4 LGTH 1.856 vs OMi 1.860 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-12-12 (differs by -FG suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): N@DRIVE: OMi Items row 1950 L 1 Size = 1.590; M5@DRIVE: OMi Items row 1950 M 2 Size = 1.750; M10@DRIVE: OMi Items row 1950 M 1 Size = 1.190; C3HEX@HEX: OMi Items row 1950 Nut Hex 1 = 1.25; Y@HEX: OMi Items row 1950 Hex Flat = 1.063; D1@BORE: OMi Items row 1950 Side 1 ID = 0.719; D@BORE: OMi Items row 1950 Side 2 ID = 0.609; THDMAJ_A@DRIVE: 3/4-14 -&gt; 1.05 (end library); THDMAJ_B@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male pipe leg (catalog N), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 ID = pipe-end bore, Side 2 ID = swivel bore (batch-15 pairing, Brennan TFA p35 letters) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1954 (= Brennan TFA p35 6501-24-24-FG, one source) - ASSUMED; catalog rounding-only prints: M10@DRIVE: catalog M4 LGTH 1.856 vs OMi 1.860 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | leg 1: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1950 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p035-t01: TUBE O.D. 3/4, A NPTF 3/4-14, B SAE 37Deg 1-1/16-12, A DRILL 0.719, B DRILL 0.609, M4 LGTH 1.180, M6 LGTH 1.750, N LGTH 1.590, C HEX 1.250, Y FLATS 1.062 | leg 1: male NPTF thread dia at L2 1.0589 vs hex flats 1.0630 (round end flush with the flats by 0.0020; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>6501-24-24-FG</t>
+          <t>6501-12-12-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6501-32-32-FG</t>
+          <t>6501-16-16-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="C12" t="n">
-        <v>1.25</v>
+        <v>0.656</v>
       </c>
       <c r="D12" t="n">
-        <v>1.16929</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7565</v>
+        <v>0.6828</v>
       </c>
       <c r="F12" t="n">
         <v>1.7899</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2735</v>
+        <v>0.2572</v>
       </c>
       <c r="H12" t="n">
-        <v>3.38</v>
+        <v>2.01</v>
       </c>
       <c r="I12" t="n">
-        <v>1.25</v>
+        <v>0.656</v>
       </c>
       <c r="J12" t="n">
-        <v>1.67</v>
+        <v>1.175</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0785</v>
+        <v>0.5485</v>
       </c>
       <c r="L12" t="n">
-        <v>1.61</v>
+        <v>1.139</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3936</v>
+        <v>0.727</v>
       </c>
       <c r="N12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4242</v>
+        <v>0.749</v>
       </c>
       <c r="P12" t="n">
-        <v>0.862</v>
+        <v>0.6564</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.65988</v>
+        <v>0.86603</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>0.65625</v>
       </c>
       <c r="S12" t="n">
-        <v>1.20489</v>
+        <v>0.61114</v>
       </c>
       <c r="T12" t="n">
-        <v>0.702</v>
+        <v>0.4873</v>
       </c>
       <c r="U12" t="n">
-        <v>1.325</v>
+        <v>0.665</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4202</v>
+        <v>0.9544</v>
       </c>
       <c r="W12" t="n">
-        <v>1.198</v>
+        <v>0.604</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1175</v>
+        <v>0.5475</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.875</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.862</v>
+        <v>0.6564</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.938</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.781</v>
+        <v>0.844</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.38</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.33859</v>
+        <v>1.2832</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.7565</v>
+        <v>0.6828</v>
       </c>
       <c r="AH12" t="n">
         <v>0.08696</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.16929</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09973</v>
+        <v>0.57203</v>
       </c>
       <c r="AK12" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.40978</v>
+        <v>1.22228</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.7399</v>
+        <v>0.5252</v>
       </c>
       <c r="AN12" t="n">
         <v>0.08333</v>
       </c>
       <c r="AO12" t="n">
+        <v>0.61114</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6501-16-16-FG</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 1-11 1/2 NPTF x 1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>6501</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-16-16 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1952 L 1 Size = 1.970 (table had empty); M5@DRIVE: OMi Items!O1952 M 2 Size = 2.010 (table had empty); M10@DRIVE: OMi Items!N1952 M 1 Size = 1.410 (table had empty); C3HEX@HEX: OMi Items!V1952 Nut Hex 1 = 1.500 (table had empty); Y@HEX: OMi Items!R1952 Hex Flat = 1.312 (table had empty); D1@BORE: OMi Items!S1952 Side 1 ID = 0.938 (table had empty); D@BORE: OMi Items!X1952 Side 2 ID = 0.844 (table had empty); THDMAJ_A@DRIVE: 1-11 1/2 -&gt; 1.315 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 1 5/16-12 -&gt; 1.3125 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-16-16-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1952 (= Brennan TFA p35 6501-16-16-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | leg 1: male NPTF thread dia at L2 1.3259 vs hex flats 1.3120 (round end proud of the flats by 0.0069; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>6501-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.9889</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.1547</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5375</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.6267</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.81335</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.74378</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.53478</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.76739</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>6501-20-20-FG</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 1 1/4-11 1/2 NPTF x 1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>6501</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-20-20 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1953 L 1 Size = 2.380 (table had empty); M5@DRIVE: OMi Items!O1953 M 2 Size = 2.310 (table had empty); M10@DRIVE: OMi Items!N1953 M 1 Size = 1.670 (table had empty); C3HEX@HEX: OMi Items!V1953 Nut Hex 1 = 2.000 (table had empty); Y@HEX: OMi Items!R1953 Hex Flat = 1.625 (table had empty); D1@BORE: OMi Items!S1953 Side 1 ID = 1.250 (table had empty); D@BORE: OMi Items!X1953 Side 2 ID = 1.078 (table had empty); THDMAJ_A@DRIVE: 1 1/4-11 1/2 -&gt; 1.66 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 1 5/8-12 -&gt; 1.625 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-20-20-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1953 (= Brennan TFA p35 6501-20-20-FG, one source) - ASSUMED; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | leg 1: male NPTF thread dia at L2 1.6709 vs hex flats 1.6250 (round end proud of the flats by 0.0229; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>6501-20-20-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.0504</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.1134</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.29904</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.065</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.78478</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.89239</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.08203</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>6501-24-24-FG</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>90 deg Male Pipe x Female Swivel Elbow, 1 1/2-11 1/2 NPTF x 1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>6501</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6501-24-24 (differs by -FG suffix) -&gt; dims NOT copied; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1954 L 1 Size = 2.640 (table had empty); M5@DRIVE: OMi Items!O1954 M 2 Size = 2.590 (table had empty); M10@DRIVE: OMi Items!N1954 M 1 Size = 1.860 (table had empty); C3HEX@HEX: OMi Items!V1954 Nut Hex 1 = 2.250 (table had empty); Y@HEX: OMi Items!R1954 Hex Flat = 1.875 (table had empty); D1@BORE: OMi Items!S1954 Side 1 ID = 1.500 (table had empty); D@BORE: OMi Items!X1954 Side 2 ID = 1.312 (table had empty); THDMAJ_A@DRIVE: 1 1/2-11 1/2 -&gt; 1.9 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 1 7/8-12 -&gt; 1.875 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-24-24-FG row = OMi on every cell (rounding only: M10@DRIVE: catalog M4 LGTH 1.856 vs OMi 1.860 - rounding only, OMi kept) - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6501-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1954 (= Brennan TFA p35 6501-24-24-FG, one source) - ASSUMED; catalog rounding-only prints: M10@DRIVE: catalog M4 LGTH 1.856 vs OMi 1.860 - rounding only, OMi kept; open, NON-gating: Q-NEW-MS51531NUT (optional routes to VERIFIED only - TaskC_resort.md 3d "never gate building": Q-NEW-MS51531NUT = MS51531D tube-nut hex as a 2nd source for the swivel nut hex) | leg 1: male NPTF thread dia at L2 1.9109 vs hex flats 1.8750 (round end proud of the flats by 0.0179; Brennan 5600-16-16-16-FG also has its round end proud of the flats, by 0.0012)</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>6501-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6501-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.65988</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S15" t="n">
         <v>1.20489</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="T15" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AQ15" t="n">
         <v>3.38</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AR15" t="n">
         <v>2.5</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AS15" t="n">
         <v>1.97</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AT15" t="n">
         <v>2.5</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AU15" t="n">
         <v>1.71</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AV15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AW15" t="n">
         <v>1.25</v>
       </c>
-      <c r="AX12" t="n">
-        <v>0.7216900000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0.7216900000000001</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.44338</v>
-      </c>
-      <c r="BA12" t="inlineStr">
+      <c r="AX15" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.72119</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.44288</v>
+      </c>
+      <c r="BA15" t="inlineStr">
         <is>
           <t>6501-32-32-FG</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>90 deg Male Pipe x Female Swivel Elbow, 2-11 1/2 NPTF x 2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>6501</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BE15" t="inlineStr">
         <is>
           <t>2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING; BATCH 15 (2026-10-02, staged): N@DRIVE: OMi Items!P1955 L 1 Size = 3.000 (table had empty); M5@DRIVE: OMi Items!O1955 M 2 Size = 3.380 (table had empty); M10@DRIVE: OMi Items!N1955 M 1 Size = 2.440 (table had empty); C3HEX@HEX: OMi Items!V1955 Nut Hex 1 = 2.875 (table had empty); Y@HEX: OMi Items!R1955 Hex Flat = 2.500 (table had empty); D1@BORE: OMi Items!S1955 Side 1 ID = 1.938 (table had empty); D@BORE: OMi Items!X1955 Side 2 ID = 1.781 (table had empty); THDMAJ_A@DRIVE: 2-11 1/2 -&gt; 2.375 (dash-correct end library: ASME B1.20.1 / ms51500.py NPTF); THDMAJ_B@DRIVE: 2 1/2-12 -&gt; 2.5 (dash-correct end library: MS33656J / gen_straight2 JIC) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED; batch 15 go-ahead user 2026-10-02 (staged)]; column pairing: OMi L 1 = catalog N (male pipe leg), M 2 = M6 (swivel-nut face), M 1 = M4 (swivel nose / seat), Hex Flat = Y FLATS, Nut Hex 1 = C HEX, Side 1 ID = A DRILL (pipe end), Side 2 ID = B DRILL (swivel end) (TFA p35 6501-FG drawing letters; Q-B-6501 answered by the catalog, 00_DOCS/Brennan_Catalog_2026-10-01.md 3.5 + impact/F1b.json / F2b.json); cross-check: Brennan TFA catalog p35 6501-32-32-FG row = OMi on every cell - same source as OMi (not a 2nd source); the non-forged Air-Way row of this size is NOT used; the generator MODEL text names the leg columns "Air-Way M5 / M10" - on this row they hold the OMi values above | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
+      <c r="BH15" t="inlineStr">
         <is>
           <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | RESOLVED 2026-10-02 (batch 15, staged for review): this -FG part's own dimensions from OMi WebsitePartsInfo2026.xlsx Items row 1955 (= Brennan TFA p35 6501-32-32-FG, one source) - ASSUMED; a second independent dimensional source is still missing</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>6501-32-32-FG</t>
         </is>

--- a/04_DESIGN_TABLES/DesignTable_6501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6501_SW2.xlsx
@@ -743,7 +743,7 @@
         <v>0.1582</v>
       </c>
       <c r="H2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="I2" t="n">
         <v>0.28</v>
@@ -812,7 +812,7 @@
         <v>0.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF2" t="n">
         <v>0.52183</v>
@@ -848,7 +848,7 @@
         <v>0.21875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AR2" t="n">
         <v>0.5600000000000001</v>
@@ -860,7 +860,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.425</v>
+        <v>0.455</v>
       </c>
       <c r="AV2" t="n">
         <v>0.28</v>
@@ -909,7 +909,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Air-Way s132 only (double-pass 16 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s132 only (double-pass 16 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1941 = 0.800 (table had 0.77) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1941 = 1.140 (table had 1.11) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): M10@DRIVE 0.77 -&gt; OMi 0.800 (Items!N1941, M127) | A19 (user 2026-10-18, group 2 settled): M5@DRIVE 1.11 -&gt; OMi 1.140 (Items!O1941, M128)</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6501_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6501_SW2.xlsx
@@ -743,7 +743,7 @@
         <v>0.1582</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="I2" t="n">
         <v>0.28</v>
@@ -812,7 +812,7 @@
         <v>0.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
         <v>0.52183</v>
@@ -848,7 +848,7 @@
         <v>0.21875</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AR2" t="n">
         <v>0.5600000000000001</v>
@@ -860,7 +860,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.455</v>
+        <v>0.425</v>
       </c>
       <c r="AV2" t="n">
         <v>0.28</v>
@@ -909,12 +909,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Air-Way s132 only (double-pass 16 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1941 = 0.800 (table had 0.77) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1941 = 1.140 (table had 1.11) [user 2026-10-18 A19] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s132 only (double-pass 16 rows); M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1941 = 0.800 (table had 0.77) [user 2026-10-18 A19]; M5@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!O1941 = 1.140 (table had 1.11) [user 2026-10-18 A19]; M5@DRIVE: Air-Way 1.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; M10@DRIVE: Air-Way 0.77 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M10@DRIVE 0.77 -&gt; OMi 0.800 (Items!N1941, M127) | A19 (user 2026-10-18, group 2 settled): M5@DRIVE 1.11 -&gt; OMi 1.140 (Items!O1941, M128)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M10@DRIVE 0.77 -&gt; OMi 0.800 (Items!N1941, M127) | A19 (user 2026-10-18, group 2 settled): M5@DRIVE 1.11 -&gt; OMi 1.140 (Items!O1941, M128) | 2026-10-20 Air-Way first: M5@DRIVE OMi/Brennan 1.14 -&gt; Air-Way 1.11 | 2026-10-20 Air-Way first: M10@DRIVE OMi/Brennan 0.8 -&gt; Air-Way 0.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
